--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -932,130 +932,6 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Bohusläns Flora 2011</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>78902762</v>
-      </c>
-      <c r="B4" t="n">
-        <v>102661</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>837</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Hedjohannesört</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Hypericum pulchrum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Solberg, 700 m NNV om byn, Boh</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>326775</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6428126</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kungälv</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Romelanda</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>OB-Kun-0127</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2019-07-13</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2019-07-13</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Roger Gahnertz</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Roger Gahnertz, Johan Hjerpe</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,12 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>101222</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>326765.7406671251</v>
+        <v>326766</v>
       </c>
       <c r="R3" t="n">
-        <v>6428111.049076904</v>
+        <v>6428111</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -884,19 +879,9 @@
           <t>1999-10-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-10-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103044</v>
+        <v>103055</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103055</v>
+        <v>103063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103063</v>
+        <v>103075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103075</v>
+        <v>103081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103081</v>
+        <v>103083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103083</v>
+        <v>103110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103110</v>
+        <v>103116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103116</v>
+        <v>103123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103123</v>
+        <v>103127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103127</v>
+        <v>103134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -814,7 +814,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103137</v>
+        <v>103142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60627540</v>
+        <v>295063</v>
       </c>
       <c r="B2" t="n">
-        <v>101222</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,22 +713,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Solberg, 700 m NNV om byn, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>326775.4388400869</v>
+        <v>326775</v>
       </c>
       <c r="R2" t="n">
-        <v>6428126.034900601</v>
+        <v>6428126</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,22 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-07-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-07-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +771,20 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>stig i barrskog</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Roger Gahnertz</t>
+          <t>Bohuslän Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Gahnertz</t>
+          <t>Bohuslän Floraväktarna, Roger Gahnertz</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -814,7 +798,7 @@
         <v>91271272</v>
       </c>
       <c r="B3" t="n">
-        <v>103142</v>
+        <v>103650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23704-2024 artfynd.xlsx
+++ b/artfynd/A 23704-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -792,6 +797,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/295063</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,8 +913,17 @@
           <t>Bohusläns Flora 2011</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91271272</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>